--- a/jpcore-r4b/develop/StructureDefinition-jp-medicationdispense.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-medicationdispense.xlsx
@@ -69,7 +69,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>No display for ContactDetail</t>
+    <t>FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) (http://jpfhir.jp, office@hlfhir.jp)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/jpcore-r4b/develop/StructureDefinition-jp-medicationdispense.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-medicationdispense.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2766" uniqueCount="488">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2766" uniqueCount="491">
   <si>
     <t>Property</t>
   </si>
@@ -1263,14 +1263,13 @@
     <t>使用状況によって、これがどのような量であるか、したがってどのような単位を使用できるかが定義される場合がかなりある。使用状況によっては、比較演算子の値も制限される場合がある。</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
-qty-3:If a code for the unit is present, the system SHALL also be present {code.empty() or system.exists()}sqty-1:The comparator is not used on a SimpleQuantity {comparator.empty()}</t>
-  </si>
-  <si>
-    <t>PQ, IVL&lt;PQ&gt;, MO, CO, depending on the values</t>
-  </si>
-  <si>
-    <t>SN (see also Range) or CQ</t>
+    <t>.quantity</t>
+  </si>
+  <si>
+    <t>CombinedMedicationDispense.SupplyEvent.quantity</t>
+  </si>
+  <si>
+    <t>RXD-4-Actual Dispense Amount / RXD-5.1-Actual Dispense Units.code / RXD-5.3-Actual Dispense Units.name of coding system</t>
   </si>
   <si>
     <t>MedicationDispense.daysSupply</t>
@@ -1280,6 +1279,15 @@
   </si>
   <si>
     <t>タイミングとして表される投薬量。すなわち、XX日分、XX回分などの数量。</t>
+  </si>
+  <si>
+    <t>effectiveUseTime</t>
+  </si>
+  <si>
+    <t>TQ1.6 Timing/Quantity Segment Service Duration.+Prior to v2.5, ORC.7.3 Common Order Segment / Quantity/Timing / Duration component.  This is a formatted string, first character for the time unit (e.g., D=days), followed by the value.  For example, “D14” represents “14 days supply”+From v2.5 on, TQ1.6 Timing/Quantity Segment / Service Duration.  This is a CQ data type (&lt;Quantity (NM)&gt; ^ &lt;Units (CWE)&gt;), thus for days supply, assuming the unit of measure is “days”, the numeric value is TQ1.6.1 (…|14^+For backwards compatibility, ORC.7 was permitted through v2.6.  Both forms (field and segment) may be present in v2.5, v2.5.1, and v2.6</t>
   </si>
   <si>
     <t>MedicationDispense.whenPrepared</t>
@@ -1387,7 +1395,10 @@
 </t>
   </si>
   <si>
-    <t>薬の服用方法・服用した方法、または服用すべき方法</t>
+    <t>How the medication is to be used by the patient or administered by the caregiver</t>
+  </si>
+  <si>
+    <t>Indicates how the medication is to be used by the patient.</t>
   </si>
   <si>
     <t>When the dose or rate is intended to change over the entire administration period (e.g. Tapering dose prescriptions), multiple instances of dosage instructions will need to be supplied to convey the different doses/rates.@@ -1894,7 +1905,7 @@
     <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
     <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
     <col min="40" max="40" width="73.296875" customWidth="true" bestFit="true"/>
-    <col min="41" max="41" width="94.375" customWidth="true" bestFit="true"/>
+    <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -8537,22 +8548,22 @@
         <v>90</v>
       </c>
       <c r="AI57" t="s" s="2">
-        <v>148</v>
+        <v>79</v>
       </c>
       <c r="AJ57" t="s" s="2">
+        <v>102</v>
+      </c>
+      <c r="AK57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AL57" t="s" s="2">
         <v>400</v>
       </c>
-      <c r="AK57" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AL57" t="s" s="2">
+      <c r="AM57" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AN57" t="s" s="2">
         <v>401</v>
-      </c>
-      <c r="AM57" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AN57" t="s" s="2">
-        <v>79</v>
       </c>
       <c r="AO57" t="s" s="2">
         <v>402</v>
@@ -8654,16 +8665,16 @@
         <v>90</v>
       </c>
       <c r="AI58" t="s" s="2">
-        <v>148</v>
+        <v>79</v>
       </c>
       <c r="AJ58" t="s" s="2">
-        <v>400</v>
+        <v>102</v>
       </c>
       <c r="AK58" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AL58" t="s" s="2">
-        <v>401</v>
+        <v>406</v>
       </c>
       <c r="AM58" t="s" s="2">
         <v>79</v>
@@ -8672,15 +8683,15 @@
         <v>79</v>
       </c>
       <c r="AO58" t="s" s="2">
-        <v>402</v>
+        <v>407</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8703,13 +8714,13 @@
         <v>91</v>
       </c>
       <c r="K59" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>408</v>
+        <v>410</v>
       </c>
       <c r="N59" s="2"/>
       <c r="O59" s="2"/>
@@ -8760,7 +8771,7 @@
         <v>79</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>406</v>
+        <v>408</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -8778,24 +8789,24 @@
         <v>79</v>
       </c>
       <c r="AL59" t="s" s="2">
-        <v>409</v>
+        <v>411</v>
       </c>
       <c r="AM59" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN59" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AO59" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -8818,13 +8829,13 @@
         <v>79</v>
       </c>
       <c r="K60" t="s" s="2">
-        <v>407</v>
+        <v>409</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>413</v>
+        <v>415</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>414</v>
+        <v>416</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" s="2"/>
@@ -8875,7 +8886,7 @@
         <v>79</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>412</v>
+        <v>414</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -8890,27 +8901,27 @@
         <v>102</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>415</v>
+        <v>417</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>416</v>
+        <v>418</v>
       </c>
       <c r="AM60" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN60" t="s" s="2">
-        <v>410</v>
+        <v>412</v>
       </c>
       <c r="AO60" t="s" s="2">
-        <v>411</v>
+        <v>413</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8936,10 +8947,10 @@
         <v>373</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>418</v>
+        <v>420</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>419</v>
+        <v>421</v>
       </c>
       <c r="N61" t="s" s="2">
         <v>328</v>
@@ -8992,7 +9003,7 @@
         <v>79</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>417</v>
+        <v>419</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9010,24 +9021,24 @@
         <v>79</v>
       </c>
       <c r="AL61" t="s" s="2">
-        <v>420</v>
+        <v>422</v>
       </c>
       <c r="AM61" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN61" t="s" s="2">
-        <v>421</v>
+        <v>423</v>
       </c>
       <c r="AO61" t="s" s="2">
-        <v>422</v>
+        <v>424</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9050,13 +9061,13 @@
         <v>79</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>424</v>
+        <v>426</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>425</v>
+        <v>427</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>426</v>
+        <v>428</v>
       </c>
       <c r="N62" t="s" s="2">
         <v>328</v>
@@ -9109,7 +9120,7 @@
         <v>79</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>423</v>
+        <v>425</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9127,13 +9138,13 @@
         <v>79</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>427</v>
+        <v>429</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN62" t="s" s="2">
-        <v>428</v>
+        <v>430</v>
       </c>
       <c r="AO62" t="s" s="2">
         <v>79</v>
@@ -9141,10 +9152,10 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9167,16 +9178,16 @@
         <v>79</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>430</v>
+        <v>432</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>431</v>
+        <v>433</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>432</v>
+        <v>434</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>433</v>
+        <v>435</v>
       </c>
       <c r="O63" s="2"/>
       <c r="P63" t="s" s="2">
@@ -9226,7 +9237,7 @@
         <v>79</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>429</v>
+        <v>431</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -9241,10 +9252,10 @@
         <v>102</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>434</v>
+        <v>436</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>435</v>
+        <v>437</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>79</v>
@@ -9253,15 +9264,15 @@
         <v>79</v>
       </c>
       <c r="AO63" t="s" s="2">
-        <v>436</v>
+        <v>438</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9284,16 +9295,16 @@
         <v>79</v>
       </c>
       <c r="K64" t="s" s="2">
-        <v>438</v>
+        <v>440</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>439</v>
+        <v>441</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>439</v>
+        <v>442</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>440</v>
+        <v>443</v>
       </c>
       <c r="O64" s="2"/>
       <c r="P64" t="s" s="2">
@@ -9343,7 +9354,7 @@
         <v>79</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>437</v>
+        <v>439</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -9361,7 +9372,7 @@
         <v>79</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>441</v>
+        <v>444</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>79</v>
@@ -9375,10 +9386,10 @@
     </row>
     <row r="65">
       <c r="A65" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9404,10 +9415,10 @@
         <v>346</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>443</v>
+        <v>446</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>444</v>
+        <v>447</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" s="2"/>
@@ -9458,7 +9469,7 @@
         <v>79</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>442</v>
+        <v>445</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -9476,13 +9487,13 @@
         <v>79</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>445</v>
+        <v>448</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN65" t="s" s="2">
-        <v>446</v>
+        <v>449</v>
       </c>
       <c r="AO65" t="s" s="2">
         <v>79</v>
@@ -9490,10 +9501,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>447</v>
+        <v>450</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9605,10 +9616,10 @@
     </row>
     <row r="67">
       <c r="A67" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>448</v>
+        <v>451</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9722,10 +9733,10 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>449</v>
+        <v>452</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9841,10 +9852,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -9867,13 +9878,13 @@
         <v>79</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>451</v>
+        <v>454</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>452</v>
+        <v>455</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>453</v>
+        <v>456</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -9924,7 +9935,7 @@
         <v>79</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>450</v>
+        <v>453</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>90</v>
@@ -9942,7 +9953,7 @@
         <v>79</v>
       </c>
       <c r="AL69" t="s" s="2">
-        <v>454</v>
+        <v>457</v>
       </c>
       <c r="AM69" t="s" s="2">
         <v>79</v>
@@ -9956,10 +9967,10 @@
     </row>
     <row r="70">
       <c r="A70" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>455</v>
+        <v>458</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9985,10 +9996,10 @@
         <v>197</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>456</v>
+        <v>459</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>457</v>
+        <v>460</v>
       </c>
       <c r="N70" s="2"/>
       <c r="O70" s="2"/>
@@ -10018,28 +10029,28 @@
         <v>301</v>
       </c>
       <c r="Y70" t="s" s="2">
+        <v>461</v>
+      </c>
+      <c r="Z70" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="AA70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE70" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF70" t="s" s="2">
         <v>458</v>
-      </c>
-      <c r="Z70" t="s" s="2">
-        <v>459</v>
-      </c>
-      <c r="AA70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE70" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF70" t="s" s="2">
-        <v>455</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>80</v>
@@ -10063,18 +10074,18 @@
         <v>79</v>
       </c>
       <c r="AN70" t="s" s="2">
-        <v>460</v>
+        <v>463</v>
       </c>
       <c r="AO70" t="s" s="2">
-        <v>461</v>
+        <v>464</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>462</v>
+        <v>465</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10100,10 +10111,10 @@
         <v>197</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>463</v>
+        <v>466</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>464</v>
+        <v>467</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -10133,28 +10144,28 @@
         <v>301</v>
       </c>
       <c r="Y71" t="s" s="2">
+        <v>468</v>
+      </c>
+      <c r="Z71" t="s" s="2">
+        <v>469</v>
+      </c>
+      <c r="AA71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AB71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AC71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AD71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AE71" t="s" s="2">
+        <v>79</v>
+      </c>
+      <c r="AF71" t="s" s="2">
         <v>465</v>
-      </c>
-      <c r="Z71" t="s" s="2">
-        <v>466</v>
-      </c>
-      <c r="AA71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AB71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AC71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AD71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AE71" t="s" s="2">
-        <v>79</v>
-      </c>
-      <c r="AF71" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>80</v>
@@ -10172,13 +10183,13 @@
         <v>79</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>467</v>
+        <v>470</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN71" t="s" s="2">
-        <v>468</v>
+        <v>471</v>
       </c>
       <c r="AO71" t="s" s="2">
         <v>79</v>
@@ -10186,10 +10197,10 @@
     </row>
     <row r="72">
       <c r="A72" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10212,13 +10223,13 @@
         <v>79</v>
       </c>
       <c r="K72" t="s" s="2">
-        <v>470</v>
+        <v>473</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>471</v>
+        <v>474</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>472</v>
+        <v>475</v>
       </c>
       <c r="N72" t="s" s="2">
         <v>328</v>
@@ -10271,7 +10282,7 @@
         <v>79</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>469</v>
+        <v>472</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>80</v>
@@ -10289,13 +10300,13 @@
         <v>79</v>
       </c>
       <c r="AL72" t="s" s="2">
-        <v>473</v>
+        <v>476</v>
       </c>
       <c r="AM72" t="s" s="2">
         <v>79</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>474</v>
+        <v>477</v>
       </c>
       <c r="AO72" t="s" s="2">
         <v>79</v>
@@ -10303,14 +10314,14 @@
     </row>
     <row r="73">
       <c r="A73" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
-        <v>476</v>
+        <v>479</v>
       </c>
       <c r="E73" s="2"/>
       <c r="F73" t="s" s="2">
@@ -10329,16 +10340,16 @@
         <v>79</v>
       </c>
       <c r="K73" t="s" s="2">
-        <v>477</v>
+        <v>480</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>478</v>
+        <v>481</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>479</v>
+        <v>482</v>
       </c>
       <c r="N73" t="s" s="2">
-        <v>480</v>
+        <v>483</v>
       </c>
       <c r="O73" s="2"/>
       <c r="P73" t="s" s="2">
@@ -10388,7 +10399,7 @@
         <v>79</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>475</v>
+        <v>478</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>80</v>
@@ -10406,7 +10417,7 @@
         <v>79</v>
       </c>
       <c r="AL73" t="s" s="2">
-        <v>481</v>
+        <v>484</v>
       </c>
       <c r="AM73" t="s" s="2">
         <v>79</v>
@@ -10420,10 +10431,10 @@
     </row>
     <row r="74">
       <c r="A74" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10446,16 +10457,16 @@
         <v>79</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>483</v>
+        <v>486</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>484</v>
+        <v>487</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>485</v>
+        <v>488</v>
       </c>
       <c r="N74" t="s" s="2">
-        <v>486</v>
+        <v>489</v>
       </c>
       <c r="O74" s="2"/>
       <c r="P74" t="s" s="2">
@@ -10505,7 +10516,7 @@
         <v>79</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>482</v>
+        <v>485</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>80</v>
@@ -10523,7 +10534,7 @@
         <v>79</v>
       </c>
       <c r="AL74" t="s" s="2">
-        <v>487</v>
+        <v>490</v>
       </c>
       <c r="AM74" t="s" s="2">
         <v>79</v>

--- a/jpcore-r4b/develop/StructureDefinition-jp-medicationdispense.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-medicationdispense.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-dev</t>
+    <t>2.0.0-dev-temp</t>
   </si>
   <si>
     <t>Name</t>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-10-31</t>
+    <t>2024-12-30</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -90,7 +90,7 @@
     <t>Copyright</t>
   </si>
   <si>
-    <t>Copyright FHIR Japanese implementation research working group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会NeXEHRS課題研究会FHIR日本実装検討WG</t>
+    <t>Copyright Japan FHIR Implementation Infrastructure Study Group in Japan Association of Medical Informatics (JAMI) 一般社団法人日本医療情報学会FHIR国内実装基盤研究会</t>
   </si>
   <si>
     <t>FHIR Version</t>
@@ -370,7 +370,7 @@
     <t>IETF language tag</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages</t>
+    <t>http://hl7.org/fhir/ValueSet/languages|4.3.0</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -649,7 +649,7 @@
     <t>extensible</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.3.0</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -667,7 +667,7 @@
     <t>Rp番号(剤グループ番号)についてのsystem値</t>
   </si>
   <si>
-    <t>ここで付番されたIDがRp番号であることを明示するためにOIDとして定義された。urn:oid:1.2.392.100495.20.3.81で固定される。</t>
+    <t>ここで付番されたIDがRp番号であることを明示するためにOID-urlとして定義された。http://jpfhir.jp/fhir/core/mhlw/IdSystem/Medication-RPGroupNumberで固定される。</t>
   </si>
   <si>
     <t>Identifier.system is always case sensitive.</t>
@@ -676,7 +676,7 @@
     <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
-    <t>urn:oid:1.2.392.100495.20.3.81</t>
+    <t>http://jpfhir.jp/fhir/core/mhlw/IdSystem/Medication-RPGroupNumber</t>
   </si>
   <si>
     <t>http://www.acme.com/identifiers/patient</t>
@@ -753,7 +753,7 @@
     <t>MedicationDispense.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization)
+    <t xml:space="preserve">Reference(Organization|4.3.0)
 </t>
   </si>
   <si>
@@ -811,7 +811,7 @@
     <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
   </si>
   <si>
-    <t>http://jpfhir.jp/fhir/core/IdSystem/resourceInstance-identifier</t>
+    <t>urn:oid:1.2.392.100495.20.3.11</t>
   </si>
   <si>
     <t>MedicationDispense.identifier:requestIdentifier.value</t>
@@ -865,10 +865,10 @@
     <t>RP番号内（剤グループ内）の連番を示すsystem値</t>
   </si>
   <si>
-    <t>剤グループ内番号の名前空間を識別するURI。固定値urn:oid:1.2.392.100495.20.3.82</t>
-  </si>
-  <si>
-    <t>urn:oid:1.2.392.100495.20.3.82</t>
+    <t>剤グループ内番号の名前空間を識別するURI。固定値 http://jpfhir.jp/fhir/core/mhlw/IdSystem/MedicationAdministrationIndex</t>
+  </si>
+  <si>
+    <t>http://jpfhir.jp/fhir/core/mhlw/IdSystem/MedicationAdministrationIndex</t>
   </si>
   <si>
     <t>MedicationDispense.identifier:orderInRp.value</t>
@@ -939,7 +939,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(DetectedIssue)</t>
+Reference(DetectedIssue|4.3.0)</t>
   </si>
   <si>
     <t>調剤が実行されなかった理由</t>
@@ -954,7 +954,7 @@
     <t>A code describing why a dispense was not performed.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationdispense-status-reason</t>
+    <t>http://hl7.org/fhir/ValueSet/medicationdispense-status-reason|4.3.0</t>
   </si>
   <si>
     <t>Event.statusReason</t>
@@ -978,7 +978,7 @@
     <t>A code describing where the dispensed medication is expected to be consumed or administered.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationdispense-category</t>
+    <t>http://hl7.org/fhir/ValueSet/medicationdispense-category|4.3.0</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=COMP].source[classCode=OBS, moodCode=EVN, code="type of medication dispense"].value</t>
@@ -1072,7 +1072,7 @@
     <t>MedicationDispense.supportingInformation</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Resource)
+    <t xml:space="preserve">Reference(Resource|4.3.0)
 </t>
   </si>
   <si>
@@ -1149,7 +1149,7 @@
     <t>A code describing the role an individual played in dispensing a medication.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationdispense-performer-function</t>
+    <t>http://hl7.org/fhir/ValueSet/medicationdispense-performer-function|4.3.0</t>
   </si>
   <si>
     <t>participation[typeCode=PRF].functionCode</t>
@@ -1526,7 +1526,7 @@
 Drug Utilization Review (DUR)Alert</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(DetectedIssue)
+    <t xml:space="preserve">Reference(DetectedIssue|4.3.0)
 </t>
   </si>
   <si>
@@ -1546,7 +1546,7 @@
     <t>MedicationDispense.eventHistory</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Provenance)
+    <t xml:space="preserve">Reference(Provenance|4.3.0)
 </t>
   </si>
   <si>
@@ -1866,17 +1866,17 @@
   <dimension ref="A1:AO74"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="53.73046875" customWidth="true" bestFit="true"/>
-    <col min="2" max="2" width="48.12109375" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="16.3125" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
-    <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
-    <col min="7" max="7" width="5.4296875" customWidth="true" bestFit="true"/>
-    <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
-    <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="46.06640625" customWidth="true" bestFit="true"/>
+    <col min="2" max="2" width="41.2578125" customWidth="true" bestFit="true"/>
+    <col min="3" max="3" width="13.984375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="4" max="4" width="34.21875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="5" max="5" width="5.80859375" customWidth="true" bestFit="true"/>
+    <col min="6" max="6" width="4.23828125" customWidth="true" bestFit="true"/>
+    <col min="7" max="7" width="4.65625" customWidth="true" bestFit="true"/>
+    <col min="8" max="8" width="13.953125" customWidth="true" bestFit="true"/>
+    <col min="9" max="9" width="11.3671875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="246.64453125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="211.453125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -1885,26 +1885,26 @@
     <col min="17" max="17" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="18" max="18" width="20.703125" customWidth="true" bestFit="true"/>
     <col min="19" max="19" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="20" max="20" width="38.2265625" customWidth="true" bestFit="true"/>
-    <col min="21" max="21" width="17.171875" customWidth="true" bestFit="true"/>
-    <col min="22" max="22" width="17.65625" customWidth="true" bestFit="true"/>
-    <col min="23" max="23" width="19.03515625" customWidth="true" bestFit="true"/>
-    <col min="24" max="24" width="18.859375" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="90.21484375" customWidth="true" bestFit="true"/>
-    <col min="26" max="26" width="71.296875" customWidth="true" bestFit="true"/>
-    <col min="27" max="27" width="6.34765625" customWidth="true" bestFit="true"/>
-    <col min="28" max="28" width="22.71875" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="42.03515625" customWidth="true" bestFit="true"/>
-    <col min="30" max="30" width="17.21484375" customWidth="true" bestFit="true"/>
-    <col min="31" max="31" width="14.4140625" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="32" max="32" width="46.84375" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="33" max="33" width="10.5546875" customWidth="true" bestFit="true" hidden="true"/>
-    <col min="34" max="34" width="11.0390625" customWidth="true" bestFit="true"/>
+    <col min="20" max="20" width="32.7734375" customWidth="true" bestFit="true"/>
+    <col min="21" max="21" width="14.72265625" customWidth="true" bestFit="true"/>
+    <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
+    <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
+    <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="77.34375" customWidth="true" bestFit="true"/>
+    <col min="26" max="26" width="61.125" customWidth="true" bestFit="true"/>
+    <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
+    <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="36.0390625" customWidth="true" bestFit="true"/>
+    <col min="30" max="30" width="14.7578125" customWidth="true" bestFit="true"/>
+    <col min="31" max="31" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="32" max="32" width="40.16015625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="33" max="33" width="9.046875" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="34" max="34" width="9.46484375" customWidth="true" bestFit="true"/>
     <col min="35" max="35" width="100.703125" customWidth="true"/>
-    <col min="37" max="37" width="29.69921875" customWidth="true" bestFit="true"/>
-    <col min="38" max="38" width="255.0" customWidth="true" bestFit="true"/>
-    <col min="39" max="39" width="36.91796875" customWidth="true" bestFit="true"/>
-    <col min="40" max="40" width="73.296875" customWidth="true" bestFit="true"/>
+    <col min="37" max="37" width="25.4609375" customWidth="true" bestFit="true"/>
+    <col min="38" max="38" width="245.42578125" customWidth="true" bestFit="true"/>
+    <col min="39" max="39" width="31.65234375" customWidth="true" bestFit="true"/>
+    <col min="40" max="40" width="62.83984375" customWidth="true" bestFit="true"/>
     <col min="41" max="41" width="255.0" customWidth="true" bestFit="true"/>
   </cols>
   <sheetData>

--- a/jpcore-r4b/develop/StructureDefinition-jp-medicationdispense.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-medicationdispense.xlsx
@@ -30,7 +30,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>2.0.0-dev-temp</t>
+    <t>2.0.0-dev</t>
   </si>
   <si>
     <t>Name</t>

--- a/jpcore-r4b/develop/StructureDefinition-jp-medicationdispense.xlsx
+++ b/jpcore-r4b/develop/StructureDefinition-jp-medicationdispense.xlsx
@@ -271,8 +271,8 @@
     <t>指定された患者・個人へ薬剤が払い出されたか払い出される予定のものを示す。これには（供給される）提供される製品についての説明や薬剤の服用に関する指示も含まれる。薬剤払い出しは薬剤オーダに対して薬局システムが対応した結果となる。</t>
   </si>
   <si>
-    <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
-dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where(((id.exists() and ('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url)))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(uri) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}mdd-1:whenHandedOver cannot be before whenPrepared {whenHandedOver.empty() or whenPrepared.empty() or whenHandedOver &gt;= whenPrepared}</t>
+    <t>dom-2:リソースが別のリソースに含まれている場合、ネストされたリソースを含めてはなりません / If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
+dom-3:リソースが別のリソースに含まれている場合、それはリソースの他の場所から参照されるか、含有リソースを参照するものとします / If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where(((id.exists() and ('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url)))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(uri) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:リソースが別のリソースに含まれている場合、meta.versionidもmeta.lastupdatedも持ってはならない。 / If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:別のリソースにリソースが含まれている場合、セキュリティラベルはありません / If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:リソースには、堅牢な管理のための叙述(Narative)が存在することが望ましい / A resource should have narrative for robust management {text.`div`.exists()}mdd-1:いつ準備されたときにハンドドーバーができないとき / whenHandedOver cannot be before whenPrepared {whenHandedOver.empty() or whenPrepared.empty() or whenHandedOver &gt;= whenPrepared}</t>
   </si>
   <si>
     <t>Event</t>
@@ -297,13 +297,13 @@
 </t>
   </si>
   <si>
-    <t>Logical id of this artifact</t>
-  </si>
-  <si>
-    <t>The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
-  </si>
-  <si>
-    <t>The only time that a resource does not have an id is when it is being submitted to the server using a create operation.</t>
+    <t>このアーティファクトの論理ID / Logical id of this artifact</t>
+  </si>
+  <si>
+    <t>リソースのURLで使用されるリソースの論理ID。割り当てられたら、この値は変更されません。 / The logical id of the resource, as used in the URL for the resource. Once assigned, this value never changes.</t>
+  </si>
+  <si>
+    <t>リソースにIDがないのは、IDが作成操作を使用してサーバーに送信されている場合です。 / The only time that a resource does not have an id is when it is being submitted to the server using a create operation.</t>
   </si>
   <si>
     <t>Resource.id</t>
@@ -316,16 +316,16 @@
 </t>
   </si>
   <si>
-    <t>Metadata about the resource</t>
-  </si>
-  <si>
-    <t>The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
+    <t>リソースに関するMetadata / Metadata about the resource</t>
+  </si>
+  <si>
+    <t>リソースに関するMetadata。これは、インフラストラクチャによって維持されるコンテンツです。コンテンツの変更は、常にリソースのバージョンの変更に関連付けられているとは限りません。 / The metadata about the resource. This is content that is maintained by the infrastructure. Changes to the content might not always be associated with version changes to the resource.</t>
   </si>
   <si>
     <t>Resource.meta</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+    <t xml:space="preserve">ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 </t>
   </si>
   <si>
@@ -336,13 +336,13 @@
 </t>
   </si>
   <si>
-    <t>A set of rules under which this content was created</t>
-  </si>
-  <si>
-    <t>A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
-  </si>
-  <si>
-    <t>Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
+    <t>このコンテンツが作成されたルールのセット / A set of rules under which this content was created</t>
+  </si>
+  <si>
+    <t>リソースが構築されたときに従った一連のルールへの参照。コンテンツの処理時に理解する必要があります。多くの場合、これは他のプロファイルなどとともに特別なルールを定義する実装ガイドへの参照です。 / A reference to a set of rules that were followed when the resource was constructed, and which must be understood when processing the content. Often, this is a reference to an implementation guide that defines the special rules along with other profiles etc.</t>
+  </si>
+  <si>
+    <t>このルールセットを主張することは、コンテンツが限られた取引パートナーのセットによってのみ理解されることを制限します。これにより、本質的に長期的にデータの有用性が制限されます。ただし、既存の健康エコシステムは非常に破壊されており、一般的に計算可能な意味でデータを定義、収集、交換する準備ができていません。可能な限り、実装者や仕様ライターはこの要素の使用を避ける必要があります。多くの場合、使用する場合、URLは、これらの特別なルールを他のプロファイル、バリューセットなどとともに叙述(Narative)の一部として定義する実装ガイドへの参照です。 / Asserting this rule set restricts the content to be only understood by a limited set of trading partners. This inherently limits the usefulness of the data in the long term. However, the existing health eco-system is highly fractured, and not yet ready to define, collect, and exchange data in a generally computable sense. Wherever possible, implementers and/or specification writers should avoid using this element. Often, when used, the URL is a reference to an implementation guide that defines these special rules as part of it's narrative along with other profiles, value sets, etc.</t>
   </si>
   <si>
     <t>Resource.implicitRules</t>
@@ -355,19 +355,19 @@
 </t>
   </si>
   <si>
-    <t>Language of the resource content</t>
-  </si>
-  <si>
-    <t>The base language in which the resource is written.</t>
-  </si>
-  <si>
-    <t>Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
+    <t>リソースコンテンツの言語 / Language of the resource content</t>
+  </si>
+  <si>
+    <t>リソースが書かれている基本言語。 / The base language in which the resource is written.</t>
+  </si>
+  <si>
+    <t>言語は、インデックス作成とアクセシビリティをサポートするために提供されます（通常、テキストから音声までのサービスなどのサービスが言語タグを使用します）。叙述(Narative)のHTML言語タグは、叙述(Narative)に適用されます。リソース上の言語タグを使用して、リソース内のデータから生成された他のプレゼンテーションの言語を指定できます。すべてのコンテンツが基本言語である必要はありません。リソース。言語は、叙述(Narative)に自動的に適用されると想定されるべきではありません。言語が指定されている場合、HTMLのDIV要素にも指定されている場合（XML：LangとHTML Lang属性の関係については、HTML5のルールを参照してください）。 / Language is provided to support indexing and accessibility (typically, services such as text to speech use the language tag). The html language tag in the narrative applies  to the narrative. The language tag on the resource may be used to specify the language of other presentations generated from the data in the resource. Not all the content has to be in the base language. The Resource.language should not be assumed to apply to the narrative automatically. If a language is specified, it should it also be specified on the div element in the html (see rules in HTML5 for information about the relationship between xml:lang and the html lang attribute).</t>
   </si>
   <si>
     <t>preferred</t>
   </si>
   <si>
-    <t>IETF language tag</t>
+    <t>IETF言語タグ / IETF language tag</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/languages|4.3.0</t>
@@ -387,13 +387,13 @@
 </t>
   </si>
   <si>
-    <t>Text summary of the resource, for human interpretation</t>
-  </si>
-  <si>
-    <t>A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
-  </si>
-  <si>
-    <t>Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
+    <t>人間の解釈のためのリソースのテキスト概要 / Text summary of the resource, for human interpretation</t>
+  </si>
+  <si>
+    <t>リソースの概要を含み、人間へのリソースの内容を表すために使用できる人間の読み取り可能な叙述(Narative)。叙述(Narative)はすべての構造化されたデータをエンコードする必要はありませんが、人間が叙述(Narative)を読むだけで「臨床的に安全」にするために十分な詳細を含める必要があります。リソースの定義は、臨床的安全を確保するために、叙述(Narative)で表現するコンテンツを定義する場合があります。 / A human-readable narrative that contains a summary of the resource and can be used to represent the content of the resource to a human. The narrative need not encode all the structured data, but is required to contain sufficient detail to make it "clinically safe" for a human to just read the narrative. Resource definitions may define what content should be represented in the narrative to ensure clinical safety.</t>
+  </si>
+  <si>
+    <t>含まれるリソースには叙述(Narative)がありません。含まれていないリソースには叙述(Narative)が必要です。場合によっては、リソースには、追加の個別のデータがほとんどまたはまったくないテキストのみがあります（すべてのMinoccur = 1要素が満たされている限り）。これは、情報がtext blob (バイナリー ラージ オブジェクト)としてキャプチャされるレガシーシステムからのデータ、またはテキストが生またはナレーションされ、エンコードされた情報が後で追加される場合に必要になる場合があります。 / Contained resources do not have narrative. Resources that are not contained SHOULD have a narrative. In some cases, a resource may only have text with little or no additional discrete data (as long as all minOccurs=1 elements are satisfied).  This may be necessary for data from legacy systems where information is captured as a "text blob" or where text is additionally entered raw or narrated and encoded information is added later.</t>
   </si>
   <si>
     <t>DomainResource.text</t>
@@ -413,19 +413,19 @@
 </t>
   </si>
   <si>
-    <t>Contained, inline Resources</t>
-  </si>
-  <si>
-    <t>These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
-  </si>
-  <si>
-    <t>This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
+    <t>インラインリソースが含まれています / Contained, inline Resources</t>
+  </si>
+  <si>
+    <t>これらのリソースには、それらを含むリソースを除いて独立した存在はありません - 独立して特定することはできず、独自の独立したトランザクションスコープを持つこともできません。 / These resources do not have an independent existence apart from the resource that contains them - they cannot be identified independently, and nor can they have their own independent transaction scope.</t>
+  </si>
+  <si>
+    <t>識別が失われると、コンテンツを適切に識別できる場合は、これを行うべきではありません。含まれるリソースには、メタ要素にプロファイルとタグがある場合がありますが、セキュリティラベルはありません。 / This should never be done when the content can be identified properly, as once identification is lost, it is extremely difficult (and context dependent) to restore it again. Contained resources may have profiles and tags In their meta elements, but SHALL NOT have security labels.</t>
   </si>
   <si>
     <t>DomainResource.contained</t>
   </si>
   <si>
-    <t xml:space="preserve">dom-r4b:Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
+    <t xml:space="preserve">dom-r4b:R4リソース内に新しいR4Bリソースを含めると、インスタンスがR4システムと共有された場合に相互運用性の問題が発生する可能性があります / Containing new R4B resources within R4 resources may cause interoperability issues if instances are shared with R4 systems {($this is Citation or $this is Evidence or $this is EvidenceReport or $this is EvidenceVariable or $this is MedicinalProductDefinition or $this is PackagedProductDefinition or $this is AdministrableProductDefinition or $this is Ingredient or $this is ClinicalUseDefinition or $this is RegulatedAuthorization or $this is SubstanceDefinition or $this is SubscriptionStatus or $this is SubscriptionTopic) implies (%resource is Citation or %resource is Evidence or %resource is EvidenceReport or %resource is EvidenceVariable or %resource is MedicinalProductDefinition or %resource is PackagedProductDefinition or %resource is AdministrableProductDefinition or %resource is Ingredient or %resource is ClinicalUseDefinition or %resource is RegulatedAuthorization or %resource is SubstanceDefinition or %resource is SubscriptionStatus or %resource is SubscriptionTopic)}
 </t>
   </si>
   <si>
@@ -455,8 +455,8 @@
     <t>DomainResource.extension</t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+    <t>ele-1:すべてのFHIR要素には、@valueまたは子要素が必要です / All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>MedicationDispense.extension:preparation</t>
@@ -479,8 +479,8 @@
 </t>
   </si>
   <si>
-    <t>ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
-ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
+    <t>ele-1:空のParametersリソースでない限り、すべてのFHIR要素には@valueまたはchildrenが必要です / All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+ext-1:両方ではなく、拡張または値[x]が必要です / Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>MedicationDispense.modifierExtension</t>
@@ -490,17 +490,18 @@
 user content</t>
   </si>
   <si>
-    <t>Extensions that cannot be ignored</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+    <t>無視できない拡張機能 / Extensions that cannot be ignored</t>
+  </si>
+  <si>
+    <t>リソースの基本的な定義の一部ではなく、それを含む要素の理解および/または含有要素の子孫の理解を変更するために使用される場合があります。通常、修飾子要素は否定または資格を提供します。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義することが許可されていますが、拡張機能の定義の一部として満たされる一連の要件があります。アプリケーションの処理リソースは、修飾子拡張機能をチェックする必要があります。
+モディファイア拡張は、リソースまたはdomainResource上の要素の意味を変更してはなりません（修飾軸自体の意味を変更することはできません）。 / May be used to represent additional information that is not part of the basic definition of the resource and that modifies the understanding of the element that contains it and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer is allowed to define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
-    <t>There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
-  </si>
-  <si>
-    <t>Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
+    <t>拡張機能を使用または定義する機関や管轄権に関係なく、アプリケーション、プロジェクト、または標準による拡張機能の使用に関連するスティグマはありません。拡張機能の使用は、FHIR仕様がすべての人にコアレベルのシンプルさを保持できるようにするものです。 / There can be no stigma associated with the use of extensions by any application, project, or standard - regardless of the institution or jurisdiction that uses or defines the extensions.  The use of extensions is what allows the FHIR specification to retain a core level of simplicity for everyone.</t>
+  </si>
+  <si>
+    <t>修飾子拡張機能により、安全に無視できる大部分の拡張機能と明確に区別できるように、安全に無視できない拡張機能が可能になります。これにより、実装者が拡張の存在を禁止する必要性を排除することにより、相互運用性が促進されます。詳細については、[修飾子拡張の定義]（拡張性.html＃modifierextension）を参照してください。 / Modifier extensions allow for extensions that *cannot* be safely ignored to be clearly distinguished from the vast majority of extensions which can be safely ignored.  This promotes interoperability by eliminating the need for implementers to prohibit the presence of extensions. For further information, see the [definition of modifier extensions](http://hl7.org/fhir/R4B/extensibility.html#modifierExtension).</t>
   </si>
   <si>
     <t>DomainResource.modifierExtension</t>
@@ -564,10 +565,10 @@
     <t>MedicationDispense.identifier.id</t>
   </si>
   <si>
-    <t>Unique id for inter-element referencing</t>
-  </si>
-  <si>
-    <t>Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
+    <t>要素間参照のための一意のID / Unique id for inter-element referencing</t>
+  </si>
+  <si>
+    <t>リソース内の要素の一意のID（内部参照用）。これは、スペースを含まない文字列値である場合があります。 / Unique id for the element within a resource (for internal references). This may be any string value that does not contain spaces.</t>
   </si>
   <si>
     <t>Element.id</t>
@@ -582,10 +583,10 @@
     <t>MedicationDispense.identifier.extension</t>
   </si>
   <si>
-    <t>Additional content defined by implementations</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
+    <t>実装で定義された追加のコンテンツ / Additional content defined by implementations</t>
+  </si>
+  <si>
+    <t>要素の基本的な定義の一部ではない追加情報を表すために使用できます。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。 / May be used to represent additional information that is not part of the basic definition of the element. To make the use of extensions safe and manageable, there is a strict set of governance  applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension.</t>
   </si>
   <si>
     <t>Extensions are always sliced by (at least) url</t>
@@ -600,16 +601,16 @@
     <t>MedicationDispense.identifier.use</t>
   </si>
   <si>
-    <t>usual | official | temp | secondary | old (If known)</t>
-  </si>
-  <si>
-    <t>The purpose of this identifier.</t>
-  </si>
-  <si>
-    <t>Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
-  </si>
-  <si>
-    <t>Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
+    <t>通常|公式|一時的|セカンダリ|古い（知られている場合） / usual | official | temp | secondary | old (If known)</t>
+  </si>
+  <si>
+    <t>このidentifierの目的。 / The purpose of this identifier.</t>
+  </si>
+  <si>
+    <t>アプリケーションは、identifierが一時的なものであると明示的に言っていない限り、永続的であると想定できます。 / Applications can assume that an identifier is permanent unless it explicitly says that it is temporary.</t>
+  </si>
+  <si>
+    <t>特定の使用のコンテキストが一連のidentifierの中から選択される適切なidentifierを許可します。 / Allows the appropriate identifier for a particular context of use to be selected from among a set of identifiers.</t>
   </si>
   <si>
     <t>required</t>
@@ -634,16 +635,16 @@
 </t>
   </si>
   <si>
-    <t>Description of identifier</t>
-  </si>
-  <si>
-    <t>A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
-  </si>
-  <si>
-    <t>This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
-  </si>
-  <si>
-    <t>Allows users to make use of identifiers when the identifier system is not known.</t>
+    <t>identifierの説明 / Description of identifier</t>
+  </si>
+  <si>
+    <t>特定の目的に使用するidentifierを決定するために使用できるidentifierのコード化されたタイプ。 / A coded type for the identifier that can be used to determine which identifier to use for a specific purpose.</t>
+  </si>
+  <si>
+    <t>この要素は、identifierの一般的なカテゴリのみを扱います。identifier。システムに対応するコードに使用しないでください。一部のidentifierは、一般的な使用法により複数のカテゴリに分類される場合があります。システムがわかっている場合、タイプは常にシステム定義の一部であるため、タイプは不要です。ただし、システムが不明なidentifierを処理する必要があることがよくあります。多くの異なるシステムが同じタイプを持っているため、タイプとシステムの間に1：1の関係はありません。 / This element deals only with general categories of identifiers.  It SHOULD not be used for codes that correspond 1..1 with the Identifier.system. Some identifiers may fall into multiple categories due to common usage.   Where the system is known, a type is unnecessary because the type is always part of the system definition. However systems often need to handle identifiers where the system is not known. There is not a 1:1 relationship between type and system, since many different systems have the same type.</t>
+  </si>
+  <si>
+    <t>identifierシステムが不明な場合、ユーザーはidentifierを使用できます。 / Allows users to make use of identifiers when the identifier system is not known.</t>
   </si>
   <si>
     <t>extensible</t>
@@ -670,10 +671,10 @@
     <t>ここで付番されたIDがRp番号であることを明示するためにOID-urlとして定義された。http://jpfhir.jp/fhir/core/mhlw/IdSystem/Medication-RPGroupNumberで固定される。</t>
   </si>
   <si>
-    <t>Identifier.system is always case sensitive.</t>
-  </si>
-  <si>
-    <t>There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
+    <t>identifier。システムは常にケースに敏感です。 / Identifier.system is always case sensitive.</t>
+  </si>
+  <si>
+    <t>identifierのセットがたくさんあります。2つのidentifierを一致させるには、どのセットを扱っているかを知る必要があります。システムは、特定の一意のidentifierセットを識別します。 / There are many sets  of identifiers.  To perform matching of two identifiers, we need to know what set we're dealing with. The system identifies a particular set of unique identifiers.</t>
   </si>
   <si>
     <t>http://jpfhir.jp/fhir/core/mhlw/IdSystem/Medication-RPGroupNumber</t>
@@ -732,10 +733,10 @@
 </t>
   </si>
   <si>
-    <t>Time period when id is/was valid for use</t>
-  </si>
-  <si>
-    <t>Time period during which identifier is/was valid for use.</t>
+    <t>IDが使用に有効だった時間期間 / Time period when id is/was valid for use</t>
+  </si>
+  <si>
+    <t>identifierが使用される/有効な期間。 / Time period during which identifier is/was valid for use.</t>
   </si>
   <si>
     <t>Identifier.period</t>
@@ -757,13 +758,13 @@
 </t>
   </si>
   <si>
-    <t>Organization that issued id (may be just text)</t>
-  </si>
-  <si>
-    <t>Organization that issued/manages the identifier.</t>
-  </si>
-  <si>
-    <t>The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
+    <t>IDを発行した組織（単なるテキストである可能性があります） / Organization that issued id (may be just text)</t>
+  </si>
+  <si>
+    <t>identifierを発行/管理する組織。 / Organization that issued/manages the identifier.</t>
+  </si>
+  <si>
+    <t>identifierは、.reference要素を省略し、割り当て組織に関する名前またはその他のテキスト情報を反映した.display要素のみを含む場合があります。 / The Identifier.assigner may omit the .reference element and only contain a .display element reflecting the name or other textual information about the assigning organization.</t>
   </si>
   <si>
     <t>Identifier.assigner</t>
@@ -787,7 +788,7 @@
     <t>薬剤をオーダする単位としての処方箋に対するID。原則として調剤の基となったMedicationRequestのIDを設定する。</t>
   </si>
   <si>
-    <t>This is a business identifier, not a resource identifier.</t>
+    <t>これはビジネスidentifierであり、リソースidentifierではありません。 / This is a business identifier, not a resource identifier.</t>
   </si>
   <si>
     <t>MedicationDispense.identifier:requestIdentifier.id</t>
@@ -805,10 +806,10 @@
     <t>MedicationDispense.identifier:requestIdentifier.system</t>
   </si>
   <si>
-    <t>The namespace for the identifier value</t>
-  </si>
-  <si>
-    <t>Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
+    <t>identifier値の名前空間 / The namespace for the identifier value</t>
+  </si>
+  <si>
+    <t>値の名前空間、つまり一意のセット値を記述するURLを確立します。 / Establishes the namespace for the value - that is, a URL that describes a set values that are unique.</t>
   </si>
   <si>
     <t>urn:oid:1.2.392.100495.20.3.11</t>
@@ -817,13 +818,13 @@
     <t>MedicationDispense.identifier:requestIdentifier.value</t>
   </si>
   <si>
-    <t>The value that is unique</t>
-  </si>
-  <si>
-    <t>The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
-  </si>
-  <si>
-    <t>If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4B/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
+    <t>一意の値 / The value that is unique</t>
+  </si>
+  <si>
+    <t>通常、identifierの部分はユーザーに関連し、システムのコンテキスト内で一意のユーザーに関連しています。 / The portion of the identifier typically relevant to the user and which is unique within the context of the system.</t>
+  </si>
+  <si>
+    <t>値が完全なURIの場合、システムはurn：ietf：rfc：3986でなければなりません。値の主な目的は、計算マッピングです。その結果、比較目的で正規化される可能性があります（例えば、有意でない白文字、ダッシュなどの削除）ヒューマンディスプレイ用の値は、[レンダリングされた値拡張]（拡張レンダリングValue.html）を使用して伝達できます。identifier。価値は、identifierの知識を使用しない限り、ケースに敏感なものとして扱われます。システムにより、プロセッサーは、非セイズに固有の処理が安全であると確信できます。 / If the value is a full URI, then the system SHALL be urn:ietf:rfc:3986.  The value's primary purpose is computational mapping.  As a result, it may be normalized for comparison purposes (e.g. removing non-significant whitespace, dashes, etc.)  A value formatted for human display can be conveyed using the [Rendered Value extension](http://hl7.org/fhir/R4B/extension-rendered-value.html). Identifier.value is to be treated as case sensitive unless knowledge of the Identifier.system allows the processer to be confident that non-case-sensitive processing is safe.</t>
   </si>
   <si>
     <t>MedicationDispense.identifier:requestIdentifier.period</t>
@@ -914,10 +915,10 @@
     <t>一連の調剤イベントの状態を指定するコード。</t>
   </si>
   <si>
-    <t>This element is labeled as a modifier because the status contains codes that mark the resource as not currently valid.</t>
-  </si>
-  <si>
-    <t>Describes the lifecycle of the dispense.</t>
+    <t>この要素は、リソースを現在有効ではないとマークするコードが含まれているため、修飾子としてラベル付けされています。 / This element is labeled as a modifier because the status contains codes that mark the resource as not currently valid.</t>
+  </si>
+  <si>
+    <t>調剤のライフサイクルを記述します。 / Describes the lifecycle of the dispense.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/medicationdispense-status|4.3.0</t>
@@ -951,7 +952,7 @@
     <t>example</t>
   </si>
   <si>
-    <t>A code describing why a dispense was not performed.</t>
+    <t>ディスペンスが実行されなかった理由を説明するコード。 / A code describing why a dispense was not performed.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/medicationdispense-status-reason|4.3.0</t>
@@ -972,10 +973,10 @@
     <t>投薬のタイプを示す（たとえば、薬剤が消費または投与されると予想される場所（つまり、入院患者または外来患者））。　入院、外来、退院、自宅など。</t>
   </si>
   <si>
-    <t>The category can be used to include where the medication is expected to be consumed or other types of dispenses.  Invariants can be used to bind to different value sets when profiling to bind.</t>
-  </si>
-  <si>
-    <t>A code describing where the dispensed medication is expected to be consumed or administered.</t>
+    <t>このカテゴリを使用して、薬が消費される場所または他の種類のディスペンスが予想される場所を含めることができます。不変剤を使用して、プロファイリングするときに異なる値セットにバインドできます。 / The category can be used to include where the medication is expected to be consumed or other types of dispenses.  Invariants can be used to bind to different value sets when profiling to bind.</t>
+  </si>
+  <si>
+    <t>分配された薬がどこで消費または投与されると予想されるコード。 / A code describing where the dispensed medication is expected to be consumed or administered.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/medicationdispense-category|4.3.0</t>
@@ -1101,7 +1102,7 @@
     <t>調剤した人を示す</t>
   </si>
   <si>
-    <t xml:space="preserve">ele-1:All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
+    <t xml:space="preserve">ele-1:空のParametersリソースでない限り、すべてのFHIR要素には@valueまたはchildrenが必要です / All FHIR elements must have a @value or children unless an empty Parameters resource {hasValue() or (children().count() &gt; id.count()) or $this is Parameters}
 </t>
   </si>
   <si>
@@ -1124,10 +1125,11 @@
 user contentmodifiers</t>
   </si>
   <si>
-    <t>Extensions that cannot be ignored even if unrecognized</t>
-  </si>
-  <si>
-    <t>May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
+    <t>認識されていなくても無視できない拡張機能 / Extensions that cannot be ignored even if unrecognized</t>
+  </si>
+  <si>
+    <t>要素の基本的な定義の一部ではなく、それが含まれている要素の理解、および/または含まれる要素の子孫の理解を変更するために使用される場合があります。通常、修飾子要素は否定または資格を提供します。拡張機能を安全で管理しやすくするために、拡張機能の定義と使用に適用される厳格なガバナンスセットがあります。実装者は拡張機能を定義できますが、拡張機能の定義の一部として満たされる一連の要件があります。アプリケーションの処理リソースは、修飾子拡張機能をチェックする必要があります。
+モディファイア拡張は、リソースまたはdomainResource上の要素の意味を変更してはなりません（修飾軸自体の意味を変更することはできません）。 / May be used to represent additional information that is not part of the basic definition of the element and that modifies the understanding of the element in which it is contained and/or the understanding of the containing element's descendants. Usually modifier elements provide negation or qualification. To make the use of extensions safe and manageable, there is a strict set of governance applied to the definition and use of extensions. Though any implementer can define an extension, there is a set of requirements that SHALL be met as part of the definition of the extension. Applications processing a resource are required to check for modifier extensions.
 Modifier extensions SHALL NOT change the meaning of any elements on Resource or DomainResource (including cannot change the meaning of modifierExtension itself).</t>
   </si>
   <si>
@@ -1137,16 +1139,16 @@
     <t>MedicationDispense.performer.function</t>
   </si>
   <si>
-    <t>Who performed the dispense and what they did</t>
-  </si>
-  <si>
-    <t>Distinguishes the type of performer in the dispense.  For example, date enterer, packager, final checker.</t>
-  </si>
-  <si>
-    <t>Allows disambiguation of the types of involvement of different performers.</t>
-  </si>
-  <si>
-    <t>A code describing the role an individual played in dispensing a medication.</t>
+    <t>誰がディスペンスを実行し、彼らがしたことを実行しました / Who performed the dispense and what they did</t>
+  </si>
+  <si>
+    <t>ディスペンスのパフォーマーのタイプを区別します。たとえば、Date Enterer、Packager、Final Checker。 / Distinguishes the type of performer in the dispense.  For example, date enterer, packager, final checker.</t>
+  </si>
+  <si>
+    <t>さまざまなパフォーマーの関与の種類の曖昧性を乱すことができます。 / Allows disambiguation of the types of involvement of different performers.</t>
+  </si>
+  <si>
+    <t>個人が薬物療法を調剤する上で果たした役割を説明するコード。 / A code describing the role an individual played in dispensing a medication.</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/ValueSet/medicationdispense-performer-function|4.3.0</t>
@@ -1162,10 +1164,10 @@
 </t>
   </si>
   <si>
-    <t>Individual who was performing</t>
-  </si>
-  <si>
-    <t>The device, practitioner, etc. who performed the action.  It should be assumed that the actor is the dispenser of the medication.</t>
+    <t>調剤をした個人 / Individual who was performing</t>
+  </si>
+  <si>
+    <t>アクションを実行したデバイス、個人など。調剤した薬のディスペンサーであると想定されるべきです。 / The device, practitioner, etc. who performed the action.  It should be assumed that the actor is the dispenser of the medication.</t>
   </si>
   <si>
     <t>Event.performer.actor</t>
@@ -1203,7 +1205,7 @@
     <t>調剤の元になった処方オーダを表すMedicationRequestリソースへの参照。</t>
   </si>
   <si>
-    <t>Maps to basedOn in Event logical model.</t>
+    <t>イベント論理モデルのベースンへのマップ。 / Maps to basedOn in Event logical model.</t>
   </si>
   <si>
     <t>Event.basedOn</t>
@@ -1230,7 +1232,7 @@
     <t>すべてのターミノロジの使用がこの一般的なパターンに適合するわけではない。場合によっては、モデルはCodeableConceptを使用せず、コーディングを直接使用して、テキスト、コーディング、翻訳、および要素間の関係とpre-coordinationとpost-coordinationの用語関係を管理するための独自の構造を提供する必要がある。</t>
   </si>
   <si>
-    <t>ActPharmacySupplyType</t>
+    <t>薬局供給タイプ / ActPharmacySupplyType</t>
   </si>
   <si>
     <t>http://terminology.hl7.org/ValueSet/v3-ActPharmacySupplyType</t>
@@ -1395,13 +1397,14 @@
 </t>
   </si>
   <si>
-    <t>How the medication is to be used by the patient or administered by the caregiver</t>
-  </si>
-  <si>
-    <t>Indicates how the medication is to be used by the patient.</t>
-  </si>
-  <si>
-    <t>When the dose or rate is intended to change over the entire administration period (e.g. Tapering dose prescriptions), multiple instances of dosage instructions will need to be supplied to convey the different doses/rates.+    <t>患者が薬をどのように使用するか、または介護者が投与する / How the medication is to be used by the patient or administered by the caregiver</t>
+  </si>
+  <si>
+    <t>患者が薬をどのように使用するかを示します。 / Indicates how the medication is to be used by the patient.</t>
+  </si>
+  <si>
+    <t>投与または速度が行政期間全体で変化することを目的としている場合（例：用量処方の先細り）、さまざまな用量/レートを伝えるために投与量の指示の複数のインスタンスを提供する必要があります。+薬剤師は、分配されている実際の製品に基づいて、投与量を分配し、更新する前に投薬順序をレビューします。 / When the dose or rate is intended to change over the entire administration period (e.g. Tapering dose prescriptions), multiple instances of dosage instructions will need to be supplied to convey the different doses/rates. The pharmacist reviews the medication order prior to dispense and updates the dosageInstruction based on the actual product being dispensed.</t>
   </si>
   <si>
@@ -1414,7 +1417,7 @@
     <t>調剤の一部として置換が行われたかどうかを示す。場合によっては、置換が期待されるが発生しない場合もあれば、置換が予期されないが発生する場合もある。このブロックは、置換が行われたか行われなかったか、およびその理由を説明する。何も指定されていない場合、置換は行われていない。</t>
   </si>
   <si>
-    <t>Indicates whether or not substitution was made as part of the dispense.  In some cases, substitution will be expected but does not happen, in other cases substitution is not expected but does happen.  This block explains what substitution did or did not happen and why.  If nothing is specified, substitution was not done.</t>
+    <t>代替が分配の一部として行われたかどうかを示します。場合によっては、代替が予想されますが、発生しませんが、他の場合には置換は予想されませんが、発生します。このブロックは、代替が何が起こったのか、起こらなかったのか、そしてその理由を説明しています。何も指定されていない場合、置換は行われませんでした。 / Indicates whether or not substitution was made as part of the dispense.  In some cases, substitution will be expected but does not happen, in other cases substitution is not expected but does happen.  This block explains what substitution did or did not happen and why.  If nothing is specified, substitution was not done.</t>
   </si>
   <si>
     <t>.outboundRelationship[typeCode=COMP].target[classCode=SUBST, moodCode=EVN]</t>
@@ -1467,7 +1470,7 @@
 N  : 置換は発生しなかったか、許可されていない。</t>
   </si>
   <si>
-    <t>ActSubstanceAdminSubstitutionCode</t>
+    <t>物質投与代替コード / ActSubstanceAdminSubstitutionCode</t>
   </si>
   <si>
     <t>http://terminology.hl7.org/ValueSet/v3-ActSubstanceAdminSubstitutionCode</t>
@@ -1488,7 +1491,7 @@
     <t>治療継続性確保のため、FP:処方方針、 OS: 在庫欠品、  RR:代替えを義務付けまたは禁止する規制要件に従った</t>
   </si>
   <si>
-    <t>SubstanceAdminSubstitutionReason</t>
+    <t>物質投与代替理由 / SubstanceAdminSubstitutionReason</t>
   </si>
   <si>
     <t>http://terminology.hl7.org/ValueSet/v3-SubstanceAdminSubstitutionReason</t>
@@ -1537,7 +1540,7 @@
 DetectedIssue リソースへの参照。</t>
   </si>
   <si>
-    <t>This element can include a detected issue that has been identified either by a decision support system or by a clinician and may include information on the steps that were taken to address the issue.</t>
+    <t>この要素には、意思決定支援システムまたは臨床医によって特定された検出された問題を含めることができ、問題に対処するために取られたプロシジャー（処置等）に関する情報を含めることができます。 / This element can include a detected issue that has been identified either by a decision support system or by a clinician and may include information on the steps that were taken to address the issue.</t>
   </si>
   <si>
     <t>.inboundRelationship[typeCode=SUBJ]/source[classCode=ALRT,moodCode=EVN].value</t>
@@ -1556,7 +1559,7 @@
     <t>調剤が確認されたときなど、発生した対象のイベントのサマリー。</t>
   </si>
   <si>
-    <t>This might not include provenances for all versions of the request – only those deemed “relevant” or important. This SHALL NOT include the Provenance associated with this current version of the resource. (If that provenance is deemed to be a “relevant” change, it will need to be added as part of a later update. Until then, it can be queried directly as the Provenance that points to this version using _revinclude All Provenances should have some historical version of this Request as their subject.).</t>
+    <t>これには、リクエストのすべてのバージョンの出所が含まれない場合があります。「関連性がある」または重要とみなされるもののみです。これには、この現在のバージョンのリソースに関連する出所を含めてはなりません。（その出所が「関連性のある」変更と見なされる場合、後の更新の一部として追加する必要があります。それまで、_revincludeを使用してこのバージョンを指す出所として直接照会することができます。この要求の歴史的バージョンは、彼らの主題として。）。 / This might not include provenances for all versions of the request – only those deemed “relevant” or important. This SHALL NOT include the Provenance associated with this current version of the resource. (If that provenance is deemed to be a “relevant” change, it will need to be added as part of a later update. Until then, it can be queried directly as the Provenance that points to this version using _revinclude All Provenances should have some historical version of this Request as their subject.).</t>
   </si>
   <si>
     <t>.inboundRelationship(typeCode=SUBJ].source[classCode=CACT, moodCode=EVN]</t>
@@ -1890,7 +1893,7 @@
     <col min="22" max="22" width="15.13671875" customWidth="true" bestFit="true"/>
     <col min="23" max="23" width="16.3203125" customWidth="true" bestFit="true"/>
     <col min="24" max="24" width="16.16796875" customWidth="true" bestFit="true"/>
-    <col min="25" max="25" width="77.34375" customWidth="true" bestFit="true"/>
+    <col min="25" max="25" width="107.16796875" customWidth="true" bestFit="true"/>
     <col min="26" max="26" width="61.125" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="5.44140625" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="19.4765625" customWidth="true" bestFit="true"/>
